--- a/invoicing/templates/JBCON_template.xlsx
+++ b/invoicing/templates/JBCON_template.xlsx
@@ -4156,9 +4156,7 @@
       <c r="B28" s="125">
         <v>0</v>
       </c>
-      <c r="C28" s="125">
-        <v>9318.2999999999993</v>
-      </c>
+      <c r="C28"/>
       <c r="D28" s="125">
         <f t="shared" si="0"/>
         <v>9318.2999999999993</v>
@@ -4178,9 +4176,7 @@
       <c r="B29" s="125">
         <v>0</v>
       </c>
-      <c r="C29" s="125">
-        <v>1494.27</v>
-      </c>
+      <c r="C29"/>
       <c r="D29" s="125">
         <f t="shared" si="0"/>
         <v>1494.27</v>
